--- a/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsCC_25.xlsx
+++ b/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsCC_25.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapDataDemo\"/>
     </mc:Choice>
@@ -26,7 +26,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="54">
   <si>
     <t>Result</t>
   </si>
@@ -172,12 +172,37 @@
   </si>
   <si>
     <t>6425</t>
+  </si>
+  <si>
+    <t>Mon Aug 24 19:55:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 31 21:21:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 02 21:48:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 02 21:54:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 20:09:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 20:23:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 20:57:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:00:30 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -560,11 +585,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
-        <v>32</v>
+      <c r="B2" t="s" s="0">
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>14</v>
@@ -654,10 +679,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -752,11 +777,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
-        <v>33</v>
+      <c r="B2" t="s" s="0">
+        <v>50</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -846,10 +871,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>34</v>
       </c>
       <c r="C2" s="3"/>
@@ -940,10 +965,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1036,7 +1061,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>39</v>
       </c>
       <c r="C2" s="3"/>
@@ -1127,11 +1152,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
-        <v>41</v>
+      <c r="B2" t="s" s="0">
+        <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -1225,10 +1250,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>36</v>
       </c>
       <c r="C2" s="3"/>
@@ -1319,10 +1344,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>37</v>
       </c>
       <c r="C2" s="3"/>
@@ -1368,7 +1393,7 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1416,10 +1441,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C2" s="3"/>

--- a/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsCC_25.xlsx
+++ b/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsCC_25.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="71">
   <si>
     <t>Result</t>
   </si>
@@ -196,6 +196,57 @@
   </si>
   <si>
     <t>Thu Sep 03 21:00:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:01:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:04:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:09:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:11:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:12:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:14:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:15:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:17:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:18:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:19:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:34:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:36:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 13:38:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:05:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:08:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:11:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 14:13:17 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -589,7 +640,7 @@
         <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>14</v>
@@ -680,10 +731,10 @@
     </row>
     <row r="2" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>24</v>
@@ -781,7 +832,7 @@
         <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -875,7 +926,7 @@
         <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -969,7 +1020,7 @@
         <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>24</v>
@@ -1156,7 +1207,7 @@
         <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -1254,7 +1305,7 @@
         <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1348,7 +1399,7 @@
         <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1445,7 +1496,7 @@
         <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsCC_25.xlsx
+++ b/KatalonData/IWPBootstrapDataDemo/VRelayPaymentsCC_25.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="76">
   <si>
     <t>Result</t>
   </si>
@@ -247,6 +247,21 @@
   </si>
   <si>
     <t>Tue Oct 20 14:13:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 01:53:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 01:55:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 01:57:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 02:10:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 27 02:37:31 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -832,7 +847,7 @@
         <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1207,7 +1222,7 @@
         <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>42</v>
@@ -1305,7 +1320,7 @@
         <v>26</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
